--- a/data_extactor/batch_10_fa/trimmed/batch_0032_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0032_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | نگارش | شنیدن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم پایه</t>
+          <t>سخن گفتن | درک مطلب | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | آموزش و تدریس | جغرافیا | فلسفه و الهیات | زبان‌های خارجی</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | آموزش و پرورش | جغرافیا | فلسفه و الهیات | زبان خارجی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>انسان‌شناسان و باستان‌شناسان | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان جغرافیای دانشگاه | استادان تاریخ دانشگاه | استادان فلسفه و دین دانشگاه | استادان علوم سیاسی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
+          <t>انسان‌شناسان و باستان‌شناسان | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | نگارش | شنیدن فعال | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | نگارش | گوش دادن فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | زبان‌های خارجی | ارتباطات و رسانه | فلسفه و الهیات</t>
+          <t>آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | تاریخ و باستان‌شناسی | زبان خارجی | ارتباطات و رسانه | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان علوم ارتباطات دانشگاه | استادان زبان و ادبیات انگلیسی دانشگاه | استادان جغرافیای دانشگاه | استادان تاریخ دانشگاه | استادان علوم سیاسی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم سیاسی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ریاضیات | آموزش و تدریس | اقتصاد و حسابداری | زبان انگلیسی</t>
+          <t>ریاضیات | آموزش و پرورش | اقتصاد و حسابداری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>استادان مدیریت و بازرگانی دانشگاه | اقتصاددانان | اقتصاددانان محیط‌زیست | استادان جغرافیای دانشگاه | استادان علوم ریاضی دانشگاه | استادان علوم سیاسی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
+          <t>استادان علوم اداری و مدیریت، آموزش عالی | اقتصاددانان | اقتصاددانان محیط زیست | استادان جغرافیای دانشگاه | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم سیاسی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نگارش | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم پایه | نظارت</t>
+          <t>نگارش | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | جغرافیا | آموزش و تدریس | تاریخ و باستان‌شناسی | ریاضیات | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>زبان انگلیسی | جغرافیا | آموزش و پرورش | تاریخ و باستان‌شناسی | ریاضیات | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان علوم جوی، زمین‌شناسی، علوم دریایی و فضا در دانشگاه | استادان علوم محیط‌زیست دانشگاه | استادان جنگل‌داری و حفاظت منابع طبیعی دانشگاه | جغرافیادانان | استادان تاریخ دانشگاه | استادان علوم سیاسی دانشگاه</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | جغرافیدانان | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم سیاسی دانشگاه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | یادگیری فعال | نگارش | شنیدن فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | درک مطلب | یادگیری فعال | نگارش | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و امور دولتی | آموزش و تدریس | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | فلسفه و الهیات</t>
+          <t>زبان انگلیسی | قانون و دولت | آموزش و پرورش | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم انتظامی و حقوق کیفری دانشگاه | استادان اقتصاد دانشگاه | استادان تاریخ دانشگاه | استادان حقوق دانشگاه | کارشناسان و تحلیل‌گران علوم سیاسی | استادان جامعه‌شناسی دانشگاه</t>
+          <t>استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | دانشمندان و پژوهشگران علوم سیاسی | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | علوم پایه | ریاضیات</t>
+          <t>راهبردهای یادگیری | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>روان‌شناسی | آموزش و تدریس | جامعه‌شناسی و انسان‌شناسی | ریاضیات | درمان و مشاوره | زیست‌شناسی</t>
+          <t>روان‌شناسی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ریاضیات | درمان و مشاوره | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>استادان علوم زیستی دانشگاه | استادان علوم تربیتی دانشگاه | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | مربیان و استادان پرستاری دانشگاه | روان‌شناسان مدرسه | استادان مددکاری اجتماعی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
+          <t>استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | مربیان و استادان پرستاری دانشگاه | روان‌شناسان مدارس | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و انسان‌شناسی | آموزش و تدریس | تاریخ و باستان‌شناسی | روان‌شناسی | فلسفه و الهیات | حقوق و امور دولتی</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | تاریخ و باستان‌شناسی | روان‌شناسی | فلسفه و الهیات | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان اقتصاد دانشگاه | استادان تاریخ دانشگاه | استادان فلسفه و دین دانشگاه | استادان علوم سیاسی دانشگاه | جامعه‌شناسان</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان اقتصاد دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه | جامعه‌شناسان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و انسان‌شناسی | آموزش و تدریس | تاریخ و باستان‌شناسی | روان‌شناسی | حقوق و امور دولتی | فلسفه و الهیات</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | تاریخ و باستان‌شناسی | روان‌شناسی | قانون و دولت | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>استادان جامعه‌شناسی دانشگاه | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | استادان اقتصاد دانشگاه | استادان جغرافیای دانشگاه | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان تاریخ دانشگاه</t>
+          <t>استادان جامعه‌شناسی دانشگاه | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | استادان اقتصاد دانشگاه | استادان جغرافیای دانشگاه | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | شنیدن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم پایه | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زیست‌شناسی | پزشکی و دندان‌پزشکی | روان‌شناسی | درمان و مشاوره | شیمی</t>
+          <t>آموزش و پرورش | زیست‌شناسی | پزشکی و دندان‌پزشکی | روان‌شناسی | درمان و مشاوره | شیمی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>استادان علوم زیستی دانشگاه | متخصصان بالینی پرستاری | کارشناسان آموزش سلامت و بهداشت | مدیران خدمات درمانی و بهداشتی | مربیان و استادان پرستاری دانشگاه | پزشکان طب پیشگیری و پزشکی اجتماعی | استادان روان‌شناسی دانشگاه</t>
+          <t>استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | پرستاران متخصص بالینی | کارشناسان آموزش بهداشت و ارتقای سلامت | مدیران خدمات درمانی و بهداشتی | مربیان و استادان پرستاری دانشگاه | متخصصان پزشکی اجتماعی و طب پیشگیری | استادان روان‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | آموزش و تدریس | روان‌شناسی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | متخصصان بالینی پرستاری | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | پرستاران متخصص دوره‌دیده (نرس پرکتیشنر) | پرستاران دارای پروانه (RN)</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران متخصص بالینی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | بهیاران و کمک‌پرستاران دارای مجوز | ماماهای پرستار | پرستاران بالینی پیشرفته | پرستاران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
